--- a/webapp/excel/Format_IP_Allocation.xlsx
+++ b/webapp/excel/Format_IP_Allocation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bcamaster\Documents\Olin\carolineapkuhuy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303FF64-4E4B-4124-A49E-989318D1FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9610D8BA-D955-49F6-A74A-CC0F857C5E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B288CA7A-192D-4051-9325-1122FF4CB7DE}"/>
   </bookViews>
